--- a/02_clean_data/46_09_Models2_aic.xlsx
+++ b/02_clean_data/46_09_Models2_aic.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\recup\Desktop\TESIS\PAPERS\01_INDIVIDUO\git_repo\Tesis_Individuo\02_clean_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66247A97-BCCB-4DA7-983F-EBD159D263C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -182,11 +190,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,7 +213,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -213,19 +228,328 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -242,507 +566,507 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>-1.61973183021064</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.16772325302486</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>-0.16772325302485999</v>
+      </c>
+      <c r="E2">
         <v>-1.97790333113062</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.478137102057303</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="F2">
+        <v>-0.47813710205730298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="n">
-        <v>-0.438592978885936</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.374301159980291</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="C3">
+        <v>-0.43859297888593601</v>
+      </c>
+      <c r="D3">
+        <v>0.37430115998029101</v>
+      </c>
+      <c r="E3">
         <v>-1.79162054252083</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>1.03695366301838</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1">
         <v>4.62365967398227</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>-1.99172717027761</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="1">
         <v>11.7190473927631</v>
       </c>
-      <c r="F4" t="n">
-        <v>-1.23621918615856</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4">
+        <v>-1.2362191861585601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.627877666324366</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>0.62787766632436603</v>
+      </c>
+      <c r="D5">
         <v>-1.8946487524928</v>
       </c>
-      <c r="E5" t="n">
-        <v>7.37642675448888</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-1.62763172431067</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5" s="1">
+        <v>7.3764267544888797</v>
+      </c>
+      <c r="F5">
+        <v>-1.6276317243106699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="n">
-        <v>4.52471972875833</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.430003978962702</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0794170437962975</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.19768580083871</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6" s="1">
+        <v>4.5247197287583303</v>
+      </c>
+      <c r="D6">
+        <v>-0.43000397896270198</v>
+      </c>
+      <c r="E6">
+        <v>7.9417043796297507E-2</v>
+      </c>
+      <c r="F6">
+        <v>1.1976858008387099</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.47980217892538</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-1.99823411416016</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.12672701245364</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="C7" s="2">
+        <v>1.4798021789253799</v>
+      </c>
+      <c r="D7">
+        <v>-1.9982341141601601</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.1267270124536402</v>
+      </c>
+      <c r="F7">
         <v>-1.99381453329374</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.5176206848073</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8" s="1">
+        <v>3.5176206848073002</v>
+      </c>
+      <c r="D8">
         <v>-1.97249556370934</v>
       </c>
-      <c r="E8" t="n">
-        <v>7.74211999038539</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" s="1">
+        <v>7.7421199903853903</v>
+      </c>
+      <c r="F8">
         <v>-1.99559300258431</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>-1.94457288371586</v>
       </c>
-      <c r="D9" t="n">
-        <v>-0.941124660825835</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9">
+        <v>-0.94112466082583501</v>
+      </c>
+      <c r="E9">
         <v>-1.26939093762508</v>
       </c>
-      <c r="F9" t="n">
-        <v>-1.91000154397983</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="F9">
+        <v>-1.9100015439798299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1">
         <v>26.0032994017288</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>-1.32673937421498</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="1">
         <v>44.6522740195146</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>-1.80312896392707</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1">
         <v>10.36435871502</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>-1.02579714127523</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="1">
         <v>23.6228370537983</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>-1.41688191181856</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" t="n">
-        <v>3.36576861595586</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.2458574920563</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="C12" s="1">
+        <v>3.3657686159558602</v>
+      </c>
+      <c r="D12">
+        <v>-1.2458574920562999</v>
+      </c>
+      <c r="E12" s="1">
         <v>10.8669182318531</v>
       </c>
-      <c r="F12" t="n">
-        <v>-0.839257946398675</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12">
+        <v>-0.83925794639867501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="n">
-        <v>8.53674294386565</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.911823835939458</v>
-      </c>
-      <c r="E13" t="n">
-        <v>20.8288631452292</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.23880874753581</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="C13" s="1">
+        <v>8.5367429438656508</v>
+      </c>
+      <c r="D13">
+        <v>-0.91182383593945804</v>
+      </c>
+      <c r="E13" s="1">
+        <v>20.828863145229199</v>
+      </c>
+      <c r="F13">
+        <v>-1.2388087475358101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="1">
         <v>3.80866012991055</v>
       </c>
-      <c r="D14" t="n">
-        <v>-1.99633089582449</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14">
+        <v>-1.9963308958244901</v>
+      </c>
+      <c r="E14" s="1">
         <v>13.4420536483528</v>
       </c>
-      <c r="F14" t="n">
-        <v>-0.944869703552058</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="F14">
+        <v>-0.94486970355205802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="n">
-        <v>4.76979293798829</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1.53528311182338</v>
-      </c>
-      <c r="E15" t="n">
-        <v>7.94334638032966</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="C15" s="1">
+        <v>4.7697929379882904</v>
+      </c>
+      <c r="D15">
+        <v>-1.5352831118233801</v>
+      </c>
+      <c r="E15" s="1">
+        <v>7.9433463803296602</v>
+      </c>
+      <c r="F15">
         <v>-1.54893414606014</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.58405857322623</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>-0.20688646477879</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.719967055056486</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1.8177141444537</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="E16">
+        <v>0.71996705505648595</v>
+      </c>
+      <c r="F16">
+        <v>-1.8177141444536999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="C17" t="n">
-        <v>-1.1056175643489</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.675310104490677</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="C17">
+        <v>-1.1056175643488999</v>
+      </c>
+      <c r="D17">
+        <v>0.67531010449067697</v>
+      </c>
+      <c r="E17">
         <v>-1.99009705482479</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>-1.66212704061212</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="n">
-        <v>6.01476509412441</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-1.01432374600392</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="C18" s="1">
+        <v>6.0147650941244102</v>
+      </c>
+      <c r="D18">
+        <v>-1.0143237460039201</v>
+      </c>
+      <c r="E18" s="1">
         <v>13.1428816158414</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>-1.96526815000465</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="n">
-        <v>-0.290608257864051</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-1.99496203378652</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="C19">
+        <v>-0.29060825786405098</v>
+      </c>
+      <c r="D19">
+        <v>-1.9949620337865199</v>
+      </c>
+      <c r="E19">
         <v>-1.4458895360508</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.111636531205107</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="n">
-        <v>22.1798424140861</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9.43519330245408</v>
-      </c>
-      <c r="E20" t="n">
-        <v>44.3155285533708</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.0172917374161443</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="C20" s="1">
+        <v>22.179842414086099</v>
+      </c>
+      <c r="D20" s="1">
+        <v>9.4351933024540795</v>
+      </c>
+      <c r="E20" s="1">
+        <v>44.315528553370797</v>
+      </c>
+      <c r="F20">
+        <v>1.7291737416144301E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="n">
-        <v>16.3586188559548</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="C21" s="1">
+        <v>16.358618855954798</v>
+      </c>
+      <c r="D21" s="1">
         <v>5.37078553292395</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="1">
         <v>29.1307075397376</v>
       </c>
-      <c r="F21" t="n">
-        <v>-1.98969813011104</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="F21">
+        <v>-1.9896981301110399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="n">
-        <v>-1.72105751376787</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="C22">
+        <v>-1.7210575137678701</v>
+      </c>
+      <c r="D22">
         <v>-1.93004568276045</v>
       </c>
-      <c r="E22" t="n">
-        <v>-0.569792289407843</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.995939727756124</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="E22">
+        <v>-0.56979228940784299</v>
+      </c>
+      <c r="F22">
+        <v>-0.99593972775612405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.973054038151432</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="C23">
+        <v>0.97305403815143199</v>
+      </c>
+      <c r="D23">
         <v>-1.99949428690764</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.761794895226217</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-1.59663956364861</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="E23">
+        <v>0.76179489522621702</v>
+      </c>
+      <c r="F23">
+        <v>-1.5966395636486099</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" t="n">
-        <v>-1.59436104254112</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-1.9832081542323</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-1.97836271875695</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-1.79599605363136</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="C24">
+        <v>-1.5943610425411201</v>
+      </c>
+      <c r="D24">
+        <v>-1.9832081542322999</v>
+      </c>
+      <c r="E24">
+        <v>-1.9783627187569499</v>
+      </c>
+      <c r="F24">
+        <v>-1.7959960536313599</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>-1.86909321344</v>
       </c>
-      <c r="D25" t="n">
-        <v>-0.674881661174617</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1.65954061119669</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1.67809285785912</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="D25">
+        <v>-0.67488166117461701</v>
+      </c>
+      <c r="E25">
+        <v>-1.6595406111966899</v>
+      </c>
+      <c r="F25">
+        <v>-1.6780928578591201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>-1.76518815029726</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>-1.88681197120057</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>-1.68836757007111</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>-1.92087195407037</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>